--- a/social_ads_tracker_template.xlsx
+++ b/social_ads_tracker_template.xlsx
@@ -241,7 +241,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +311,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC9DFC2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -320,15 +336,15 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1F3B21"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF2F5233"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B21"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -354,7 +370,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,7 +380,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5233"/>
-        <bgColor rgb="FF555555"/>
+        <bgColor rgb="FF1F3B21"/>
       </patternFill>
     </fill>
     <fill>
@@ -375,18 +391,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4C7A47"/>
-        <bgColor rgb="FF555555"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFFFFDE7"/>
+        <fgColor rgb="FFDCEAD5"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -406,6 +416,52 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF4C7A47"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FF4C7A47"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F5233"/>
       </bottom>
       <diagonal/>
     </border>
@@ -435,7 +491,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -488,24 +544,48 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -550,7 +630,7 @@
       <rgbColor rgb="FF93A9CE"/>
       <rgbColor rgb="FFAB4744"/>
       <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FFEFF5EC"/>
+      <rgbColor rgb="FFC9DFC2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFDC853E"/>
       <rgbColor rgb="FF0066CC"/>
@@ -565,14 +645,14 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDCEAD5"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF4672A8"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF6E9B5E"/>
       <rgbColor rgb="FF8AA64F"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -582,11 +662,11 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF4299B0"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF2F5233"/>
       <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FFC0504D"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF2F5233"/>
+      <rgbColor rgb="FF1F3B21"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -742,12 +822,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -766,12 +847,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -790,12 +872,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -814,12 +897,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -838,12 +922,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -862,12 +947,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="6"/>
@@ -886,12 +972,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -908,12 +995,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -1081,10 +1169,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1169,11 +1259,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="56727319"/>
-        <c:axId val="28553355"/>
+        <c:axId val="5240572"/>
+        <c:axId val="340510"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56727319"/>
+        <c:axId val="5240572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1205,7 +1295,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28553355"/>
+        <c:crossAx val="340510"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1213,7 +1303,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28553355"/>
+        <c:axId val="340510"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1255,7 +1345,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56727319"/>
+        <c:crossAx val="5240572"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1368,10 +1458,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1506,10 +1598,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c0504d"/>
+              <a:srgbClr val="6e9b5e"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="6e9b5e"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1630,11 +1724,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="65967627"/>
-        <c:axId val="43626230"/>
+        <c:axId val="98751749"/>
+        <c:axId val="45207535"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="65967627"/>
+        <c:axId val="98751749"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1666,7 +1760,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43626230"/>
+        <c:crossAx val="45207535"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1674,7 +1768,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43626230"/>
+        <c:axId val="45207535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1750,7 +1844,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65967627"/>
+        <c:crossAx val="98751749"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1808,14 +1902,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>564480</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1823,7 +1917,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7201080" y="1800360"/>
+        <a:off x="7201080" y="2104920"/>
         <a:ext cx="3599640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1838,14 +1932,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>525240</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1853,7 +1947,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="12512520" y="1800360"/>
+        <a:off x="12512520" y="2104920"/>
         <a:ext cx="4319640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1868,14 +1962,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>55080</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1883,7 +1977,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5689440" y="3895560"/>
+        <a:off x="5689440" y="4200480"/>
         <a:ext cx="6119640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -7514,82 +7608,88 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="17" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="n">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="20" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="21" t="n">
         <f aca="false">IFERROR(B6/A6,0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="22" t="n">
         <f aca="false">IFERROR(SUMIFS('Campaign Data'!$F$3:$F$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)/SUMIFS('Campaign Data'!$E$3:$E$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3),0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">IFERROR(A6/SUMIFS('Campaign Data'!$F$3:$F$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3),0)</f>
         <v>0</v>
       </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
@@ -7597,16 +7697,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="23" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7614,15 +7714,15 @@
       <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$B$3:$B$152,"Meta (Facebook/Instagram)",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$B$3:$B$152,"Meta (Facebook/Instagram)",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="25" t="n">
         <f aca="false">IFERROR(C11/B11,0)</f>
         <v>0</v>
       </c>
@@ -7631,15 +7731,15 @@
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$B$3:$B$152,"TikTok",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$B$3:$B$152,"TikTok",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">IFERROR(C12/B12,0)</f>
         <v>0</v>
       </c>
@@ -7648,15 +7748,15 @@
       <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$B$3:$B$152,"Google",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$B$3:$B$152,"Google",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="25" t="n">
         <f aca="false">IFERROR(C13/B13,0)</f>
         <v>0</v>
       </c>
@@ -7665,15 +7765,15 @@
       <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$B$3:$B$152,"Pinterest",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$B$3:$B$152,"Pinterest",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="25" t="n">
         <f aca="false">IFERROR(C14/B14,0)</f>
         <v>0</v>
       </c>
@@ -7682,15 +7782,15 @@
       <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$B$3:$B$152,"Etsy Ads",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$B$3:$B$152,"Etsy Ads",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
         <v>0</v>
       </c>
@@ -7699,15 +7799,15 @@
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$B$3:$B$152,"Other",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$B$3:$B$152,"Other",'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="25" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
         <v>0</v>
       </c>
@@ -7718,13 +7818,13 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="23" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7732,11 +7832,11 @@
       <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,1)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,1)</f>
         <v>0</v>
       </c>
@@ -7745,11 +7845,11 @@
       <c r="A23" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,2)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="18" t="n">
+      <c r="C23" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,2)</f>
         <v>0</v>
       </c>
@@ -7758,11 +7858,11 @@
       <c r="A24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,3)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,3)</f>
         <v>0</v>
       </c>
@@ -7771,11 +7871,11 @@
       <c r="A25" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,4)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,4)</f>
         <v>0</v>
       </c>
@@ -7784,11 +7884,11 @@
       <c r="A26" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,5)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,5)</f>
         <v>0</v>
       </c>
@@ -7797,11 +7897,11 @@
       <c r="A27" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,6)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,6)</f>
         <v>0</v>
       </c>
@@ -7810,11 +7910,11 @@
       <c r="A28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,7)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,7)</f>
         <v>0</v>
       </c>
@@ -7823,11 +7923,11 @@
       <c r="A29" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,8)</f>
         <v>0</v>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,8)</f>
         <v>0</v>
       </c>
@@ -7836,11 +7936,11 @@
       <c r="A30" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,9)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C30" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,9)</f>
         <v>0</v>
       </c>
@@ -7849,11 +7949,11 @@
       <c r="A31" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,10)</f>
         <v>0</v>
       </c>
-      <c r="C31" s="18" t="n">
+      <c r="C31" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,10)</f>
         <v>0</v>
       </c>
@@ -7862,11 +7962,11 @@
       <c r="A32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,11)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="18" t="n">
+      <c r="C32" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,11)</f>
         <v>0</v>
       </c>
@@ -7875,11 +7975,11 @@
       <c r="A33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$D$3:$D$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,12)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="18" t="n">
+      <c r="C33" s="24" t="n">
         <f aca="false">SUMIFS('Campaign Data'!$H$3:$H$152,'Campaign Data'!$M$3:$M$152,$B$3,'Campaign Data'!$N$3:$N$152,12)</f>
         <v>0</v>
       </c>
@@ -7942,7 +8042,7 @@
       <c r="A4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="26" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7950,7 +8050,7 @@
       <c r="A5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="26" t="s">
         <v>61</v>
       </c>
     </row>
@@ -7958,7 +8058,7 @@
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7966,7 +8066,7 @@
       <c r="A7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="26" t="s">
         <v>65</v>
       </c>
     </row>
@@ -7974,7 +8074,7 @@
       <c r="A8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="26" t="s">
         <v>67</v>
       </c>
     </row>
